--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-radiology-impression.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-radiology-impression.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -623,10 +623,279 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>imaging</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -675,69 +944,12 @@
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
   </si>
   <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -747,146 +959,25 @@
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
     <t>Observation.code.coding.version</t>
   </si>
   <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.code.coding.code</t>
   </si>
   <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>19005-8</t>
   </si>
   <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
     <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Observation.code.text</t>
-  </si>
-  <si>
-    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1170,10 +1261,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1885,7 +1973,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -3636,13 +3724,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>83</v>
@@ -3698,16 +3786,14 @@
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>188</v>
@@ -3734,10 +3820,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3745,18 +3831,18 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>94</v>
@@ -3768,23 +3854,19 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>83</v>
       </c>
@@ -3808,34 +3890,34 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>94</v>
@@ -3844,44 +3926,44 @@
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>83</v>
@@ -3893,15 +3975,17 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3938,31 +4022,31 @@
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>83</v>
@@ -3974,7 +4058,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -3985,14 +4069,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4008,21 +4092,23 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>141</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4058,19 +4144,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4082,7 +4168,7 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -4091,10 +4177,10 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4105,10 +4191,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4119,7 +4205,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4128,23 +4214,19 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4192,19 +4274,19 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4213,10 +4295,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4227,21 +4309,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4253,15 +4335,17 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4298,31 +4382,31 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4334,7 +4418,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4345,21 +4429,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4368,27 +4452,29 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4418,31 +4504,31 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>83</v>
@@ -4451,10 +4537,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4465,10 +4551,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4491,26 +4577,24 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4552,7 +4636,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4573,10 +4657,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4587,10 +4671,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4598,7 +4682,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>94</v>
@@ -4613,24 +4697,24 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>114</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>83</v>
+        <v>240</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>83</v>
@@ -4672,7 +4756,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4693,10 +4777,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4707,10 +4791,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4733,24 +4817,24 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4792,7 +4876,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4813,10 +4897,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4827,10 +4911,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4853,17 +4937,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4912,7 +4998,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4933,10 +5019,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4947,10 +5033,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4973,19 +5059,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>199</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5034,7 +5120,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5055,10 +5141,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5069,21 +5155,23 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>83</v>
@@ -5092,22 +5180,22 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>192</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5132,13 +5220,11 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5156,13 +5242,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>188</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5177,13 +5263,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5191,10 +5277,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5208,29 +5294,25 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>200</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5278,7 +5360,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5290,22 +5372,22 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>286</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5313,14 +5395,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5336,19 +5418,19 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>141</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>293</v>
+        <v>143</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5386,19 +5468,19 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5410,7 +5492,7 @@
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -5419,13 +5501,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>294</v>
+        <v>203</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5433,21 +5515,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>209</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -5459,19 +5541,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>211</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>299</v>
+        <v>213</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>300</v>
+        <v>214</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5520,13 +5602,13 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
@@ -5535,19 +5617,19 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>216</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5555,14 +5637,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>306</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5578,23 +5660,19 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5642,7 +5720,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5654,22 +5732,22 @@
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5677,21 +5755,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5700,19 +5778,19 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>140</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>141</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>143</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5750,31 +5828,31 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>208</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5783,13 +5861,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5797,10 +5875,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5808,10 +5886,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5823,26 +5901,26 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>221</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>222</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>325</v>
+        <v>223</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>224</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5884,13 +5962,13 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
@@ -5899,19 +5977,19 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>329</v>
+        <v>228</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5919,10 +5997,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>229</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5936,7 +6014,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>83</v>
@@ -5945,20 +6023,18 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>230</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>231</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6006,7 +6082,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6015,7 +6091,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -6024,27 +6100,27 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>338</v>
+        <v>235</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6052,7 +6128,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
@@ -6064,22 +6140,20 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6104,13 +6178,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6128,7 +6202,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>241</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6137,7 +6211,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6149,10 +6223,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>137</v>
+        <v>242</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>348</v>
+        <v>243</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6163,21 +6237,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>349</v>
+        <v>244</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6186,22 +6260,20 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>245</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>353</v>
+        <v>247</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6226,13 +6298,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>354</v>
+        <v>83</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>355</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6250,13 +6322,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>349</v>
+        <v>248</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6268,27 +6340,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>357</v>
+        <v>249</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>358</v>
+        <v>250</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6299,7 +6371,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6308,22 +6380,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>362</v>
+        <v>253</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>362</v>
+        <v>254</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>363</v>
+        <v>255</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>364</v>
+        <v>256</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6372,13 +6444,13 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -6393,10 +6465,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>258</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>259</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6407,10 +6479,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6430,21 +6502,23 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>261</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>262</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6468,13 +6542,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6492,7 +6566,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>265</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6510,35 +6584,35 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>266</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>374</v>
+        <v>267</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>94</v>
@@ -6550,22 +6624,22 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>377</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>286</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>379</v>
+        <v>288</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6590,13 +6664,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>381</v>
+        <v>291</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6614,10 +6688,10 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>376</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>94</v>
@@ -6629,30 +6703,30 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>382</v>
+        <v>294</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>295</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6675,17 +6749,15 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>385</v>
+        <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>386</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6734,7 +6806,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>384</v>
+        <v>202</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6746,44 +6818,44 @@
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>203</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6795,16 +6867,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>393</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>141</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>394</v>
+        <v>205</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>395</v>
+        <v>143</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6842,57 +6914,57 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>398</v>
+        <v>203</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6912,22 +6984,22 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>401</v>
+        <v>210</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>211</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>212</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>403</v>
+        <v>213</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>404</v>
+        <v>214</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6976,7 +7048,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6988,7 +7060,7 @@
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>405</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6997,10 +7069,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>406</v>
+        <v>216</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>407</v>
+        <v>217</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7011,10 +7083,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>301</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7037,13 +7109,13 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7094,7 +7166,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7118,7 +7190,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7129,10 +7201,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>409</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>302</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7161,7 +7233,7 @@
         <v>141</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>143</v>
@@ -7202,19 +7274,19 @@
         <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7238,7 +7310,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7249,52 +7321,52 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>221</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>222</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7336,19 +7408,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>414</v>
+        <v>226</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7357,10 +7429,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7371,10 +7443,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>305</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7394,18 +7466,20 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>416</v>
+        <v>199</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>417</v>
+        <v>230</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7454,7 +7528,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>415</v>
+        <v>233</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7463,7 +7537,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7475,10 +7549,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>420</v>
+        <v>234</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>421</v>
+        <v>235</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7489,10 +7563,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>306</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>306</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7512,25 +7586,27 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>416</v>
+        <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>237</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>238</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -7572,7 +7648,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>241</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7581,7 +7657,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7593,10 +7669,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>420</v>
+        <v>242</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7607,10 +7683,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>308</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7630,22 +7706,20 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>427</v>
+        <v>245</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>247</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7670,13 +7744,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7694,7 +7768,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>248</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7712,13 +7786,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>434</v>
+        <v>249</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>358</v>
+        <v>250</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7729,10 +7803,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>435</v>
+        <v>309</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
+        <v>309</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7743,7 +7817,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7752,22 +7826,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>436</v>
+        <v>253</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>437</v>
+        <v>254</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>438</v>
+        <v>255</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>256</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7792,13 +7866,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>441</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7816,13 +7890,13 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>257</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>83</v>
@@ -7834,13 +7908,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>434</v>
+        <v>258</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>358</v>
+        <v>259</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7851,10 +7925,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>310</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7874,20 +7948,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>443</v>
+        <v>199</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>444</v>
+        <v>261</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>446</v>
+        <v>264</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7936,7 +8012,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>442</v>
+        <v>265</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7957,10 +8033,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>447</v>
+        <v>267</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7971,10 +8047,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>311</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>311</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7988,25 +8064,29 @@
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>211</v>
+        <v>312</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>313</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8054,7 +8134,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>311</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8069,19 +8149,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>420</v>
+        <v>317</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>451</v>
+        <v>318</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8089,10 +8169,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8115,16 +8195,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>453</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>455</v>
+        <v>323</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8174,7 +8254,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8195,13 +8275,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>456</v>
+        <v>294</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>457</v>
+        <v>324</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8209,21 +8289,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>325</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8235,18 +8315,20 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>328</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>459</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8294,13 +8376,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>325</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8309,19 +8391,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>456</v>
+        <v>332</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>461</v>
+        <v>333</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8329,21 +8411,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>462</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>462</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8355,19 +8437,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>337</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>463</v>
+        <v>338</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
+        <v>338</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>464</v>
+        <v>339</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>465</v>
+        <v>340</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8416,13 +8498,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>462</v>
+        <v>335</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8431,19 +8513,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>466</v>
+        <v>342</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>467</v>
+        <v>343</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8451,10 +8533,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>468</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>468</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8474,18 +8556,20 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>211</v>
+        <v>346</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>212</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8534,7 +8618,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>214</v>
+        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8546,7 +8630,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8555,13 +8639,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>215</v>
+        <v>350</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8569,14 +8653,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>469</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>469</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8592,21 +8676,23 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>140</v>
+        <v>353</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>141</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8654,7 +8740,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>221</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8666,22 +8752,22 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>215</v>
+        <v>359</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8689,45 +8775,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>470</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>470</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>413</v>
+        <v>362</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>143</v>
+        <v>363</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>149</v>
+        <v>364</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8776,45 +8862,45 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>137</v>
+        <v>368</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>83</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8822,7 +8908,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>94</v>
@@ -8834,22 +8920,22 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>472</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>473</v>
+        <v>371</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>474</v>
+        <v>372</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8874,13 +8960,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>201</v>
+        <v>374</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>202</v>
+        <v>375</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>203</v>
+        <v>376</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8898,16 +8984,16 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8916,16 +9002,16 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>475</v>
+        <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>207</v>
+        <v>378</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -8933,21 +9019,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -8956,22 +9042,22 @@
         <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>477</v>
+        <v>189</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>479</v>
+        <v>381</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>480</v>
+        <v>382</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>334</v>
+        <v>383</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -8996,13 +9082,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9020,13 +9106,13 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
@@ -9038,27 +9124,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>337</v>
+        <v>387</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>339</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>482</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>482</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9069,7 +9155,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -9081,19 +9167,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>189</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>484</v>
+        <v>392</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>485</v>
+        <v>393</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9118,13 +9204,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9142,16 +9228,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>482</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9163,10 +9249,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>137</v>
+        <v>395</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9177,21 +9263,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9206,17 +9292,15 @@
         <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>487</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>488</v>
+        <v>398</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9240,13 +9324,11 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9264,13 +9346,13 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>486</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
@@ -9282,27 +9364,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>359</v>
+        <v>404</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9313,7 +9395,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9325,19 +9407,19 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>492</v>
+        <v>406</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>493</v>
+        <v>406</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>494</v>
+        <v>407</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>495</v>
+        <v>408</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9362,13 +9444,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9386,13 +9468,13 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>491</v>
+        <v>405</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
@@ -9407,20 +9489,2792 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP62">
+  <autoFilter ref="A1:AP85">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9430,7 +12284,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-radiology-impression.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-radiology-impression.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3295" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="527">
   <si>
     <t>Property</t>
   </si>
@@ -614,13 +614,16 @@
     <t>このObservationを分類するコード</t>
   </si>
   <si>
-    <t>このObservationを分類するコード。(imaging)が指定される。</t>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -636,6 +639,27 @@
     <t>FiveWs.class</t>
   </si>
   <si>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
+  </si>
+  <si>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>このObservationを分類するコード。(imaging)が指定される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
     <t>Observation.category.id</t>
   </si>
   <si>
@@ -655,6 +679,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
@@ -671,6 +698,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
     <t>Observation.category.coding</t>
   </si>
   <si>
@@ -699,12 +729,21 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
     <t>Observation.category.coding.system</t>
   </si>
   <si>
@@ -732,6 +771,9 @@
     <t>./codeSystem</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
     <t>Observation.category.coding.version</t>
   </si>
   <si>
@@ -753,6 +795,9 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
     <t>Observation.category.coding.code</t>
   </si>
   <si>
@@ -777,6 +822,9 @@
     <t>./code</t>
   </si>
   <si>
+    <t>Observation.category:first.coding.display</t>
+  </si>
+  <si>
     <t>Observation.category.coding.display</t>
   </si>
   <si>
@@ -796,6 +844,9 @@
   </si>
   <si>
     <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -826,6 +877,9 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Observation.category:first.text</t>
+  </si>
+  <si>
     <t>Observation.category.text</t>
   </si>
   <si>
@@ -848,54 +902,6 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.category:first</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>検査の第1カテゴリはJP_SimpleObservationCategory_VSから値を指定する。</t>
-  </si>
-  <si>
-    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Observation.category:first.id</t>
-  </si>
-  <si>
-    <t>Observation.category:first.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:first.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1973,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP85"/>
+  <dimension ref="A1:AP74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -3730,7 +3736,7 @@
         <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>83</v>
@@ -3776,24 +3782,26 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>188</v>
@@ -3820,10 +3828,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3831,24 +3839,26 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -3857,16 +3867,20 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
       </c>
@@ -3890,13 +3904,11 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3914,19 +3926,19 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>83</v>
@@ -3938,10 +3950,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3949,21 +3961,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>83</v>
@@ -3975,17 +3987,15 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -4022,31 +4032,31 @@
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>83</v>
@@ -4058,7 +4068,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4069,14 +4079,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4092,23 +4102,21 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4144,19 +4152,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4168,7 +4176,7 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -4177,10 +4185,10 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4194,7 +4202,7 @@
         <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4205,7 +4213,7 @@
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4214,19 +4222,23 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4274,19 +4286,19 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4295,10 +4307,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4309,21 +4321,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4335,17 +4347,15 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4382,31 +4392,31 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4418,7 +4428,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4429,21 +4439,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4452,29 +4462,27 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4504,31 +4512,31 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>83</v>
@@ -4537,10 +4545,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4551,10 +4559,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4562,7 +4570,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4577,24 +4585,26 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4636,7 +4646,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4657,10 +4667,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4671,10 +4681,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4682,7 +4692,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>94</v>
@@ -4697,24 +4707,24 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>83</v>
@@ -4756,7 +4766,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4777,10 +4787,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4791,10 +4801,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4802,7 +4812,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4817,24 +4827,24 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4876,7 +4886,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4897,10 +4907,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4911,10 +4921,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4937,19 +4947,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4998,7 +5006,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5019,10 +5027,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5033,10 +5041,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5059,19 +5067,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5120,7 +5128,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5141,10 +5149,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5155,24 +5163,22 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5180,22 +5186,22 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5220,11 +5226,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5242,13 +5250,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>188</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5263,13 +5271,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>196</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5277,18 +5285,18 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>94</v>
@@ -5300,19 +5308,23 @@
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5336,13 +5348,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5360,10 +5372,10 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>94</v>
@@ -5372,44 +5384,44 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5421,17 +5433,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5468,31 +5478,31 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -5504,7 +5514,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5515,14 +5525,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5538,23 +5548,21 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5590,19 +5598,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5614,7 +5622,7 @@
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>83</v>
@@ -5623,10 +5631,10 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5637,10 +5645,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5651,7 +5659,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5660,19 +5668,23 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5720,19 +5732,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5741,10 +5753,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5755,21 +5767,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>219</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5781,17 +5793,15 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5828,31 +5838,31 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5864,7 +5874,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5875,21 +5885,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5898,29 +5908,27 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5950,31 +5958,31 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5983,10 +5991,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5997,10 +6005,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6023,24 +6031,26 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6082,7 +6092,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6103,10 +6113,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6117,10 +6127,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6128,7 +6138,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
@@ -6143,18 +6153,18 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6202,7 +6212,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6223,10 +6233,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6237,10 +6247,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6263,24 +6273,24 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>199</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6322,7 +6332,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6343,10 +6353,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6357,10 +6367,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6383,19 +6393,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6444,7 +6452,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6465,10 +6473,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6479,10 +6487,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6505,19 +6513,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6566,7 +6574,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6587,10 +6595,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6601,18 +6609,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>94</v>
@@ -6627,19 +6635,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6664,13 +6672,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6688,10 +6696,10 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>94</v>
@@ -6703,30 +6711,30 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6740,25 +6748,29 @@
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>199</v>
+        <v>314</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>200</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6806,7 +6818,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>202</v>
+        <v>313</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6818,22 +6830,22 @@
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6841,14 +6853,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6864,19 +6876,19 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>140</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>141</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>205</v>
+        <v>324</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>143</v>
+        <v>325</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6914,19 +6926,19 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6938,7 +6950,7 @@
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6947,13 +6959,13 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6961,21 +6973,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6987,19 +6999,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>210</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>211</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>213</v>
+        <v>331</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>214</v>
+        <v>332</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7048,13 +7060,13 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>327</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
@@ -7063,19 +7075,19 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>217</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7083,14 +7095,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7106,19 +7118,23 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>199</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7166,7 +7182,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7178,22 +7194,22 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>203</v>
+        <v>345</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7201,21 +7217,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7224,19 +7240,19 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>140</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>141</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>143</v>
+        <v>350</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7274,31 +7290,31 @@
         <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7307,13 +7323,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>203</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7321,10 +7337,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7335,7 +7351,7 @@
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7347,26 +7363,26 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>108</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>221</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>222</v>
+        <v>356</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>224</v>
+        <v>358</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -7408,13 +7424,13 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>226</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
@@ -7423,19 +7439,19 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>228</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7443,10 +7459,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7460,7 +7476,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>83</v>
@@ -7469,18 +7485,20 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>230</v>
+        <v>364</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7528,7 +7546,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>233</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7537,7 +7555,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7546,27 +7564,27 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>234</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>235</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7586,27 +7604,29 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>237</v>
+        <v>373</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>239</v>
+        <v>375</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -7624,13 +7644,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7648,7 +7668,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>241</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7657,7 +7677,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7669,10 +7689,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>242</v>
+        <v>137</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>243</v>
+        <v>380</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7683,21 +7703,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7706,20 +7726,22 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>245</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>247</v>
+        <v>385</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7744,13 +7766,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7768,13 +7790,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>248</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7786,27 +7808,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>249</v>
+        <v>389</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>250</v>
+        <v>390</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7817,7 +7839,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7826,22 +7848,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>252</v>
+        <v>393</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>253</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>254</v>
+        <v>394</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>255</v>
+        <v>395</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7890,13 +7912,13 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>257</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>83</v>
@@ -7911,10 +7933,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>258</v>
+        <v>397</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>259</v>
+        <v>398</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7925,10 +7947,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7948,23 +7970,21 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>261</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7988,13 +8008,11 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8012,7 +8030,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>265</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8030,27 +8048,27 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>266</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>267</v>
+        <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8064,28 +8082,28 @@
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>312</v>
+        <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>313</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>313</v>
+        <v>408</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>314</v>
+        <v>409</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>315</v>
+        <v>410</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8110,13 +8128,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>412</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8134,7 +8152,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8149,19 +8167,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>317</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>414</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8169,10 +8187,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>415</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>415</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8183,7 +8201,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8192,19 +8210,19 @@
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>321</v>
+        <v>416</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>323</v>
+        <v>418</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8254,13 +8272,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>415</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8272,31 +8290,31 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>294</v>
+        <v>420</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>326</v>
+        <v>83</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8312,23 +8330,21 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>327</v>
+        <v>424</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>425</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8376,7 +8392,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8391,41 +8407,41 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>428</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>333</v>
+        <v>429</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8434,22 +8450,22 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>337</v>
+        <v>432</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>433</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>433</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>339</v>
+        <v>434</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>340</v>
+        <v>435</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8498,34 +8514,34 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>342</v>
+        <v>437</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>343</v>
+        <v>438</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8533,10 +8549,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>439</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>439</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8556,20 +8572,18 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>346</v>
+        <v>207</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>347</v>
+        <v>208</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8618,7 +8632,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>210</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8630,7 +8644,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8639,13 +8653,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>211</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -8653,14 +8667,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>440</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8676,23 +8690,21 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>354</v>
+        <v>214</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8740,7 +8752,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8752,22 +8764,22 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>359</v>
+        <v>211</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8775,45 +8787,45 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>361</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>443</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>363</v>
+        <v>143</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>364</v>
+        <v>149</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8862,45 +8874,45 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>445</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8923,20 +8935,16 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>189</v>
+        <v>447</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8960,13 +8968,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8984,7 +8992,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8993,7 +9001,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>377</v>
+        <v>450</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9005,10 +9013,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>451</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>378</v>
+        <v>452</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9019,21 +9027,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>453</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -9045,20 +9053,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>189</v>
+        <v>447</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>381</v>
+        <v>454</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9082,13 +9086,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9106,16 +9110,16 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9124,27 +9128,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9155,7 +9159,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -9167,19 +9171,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>391</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>392</v>
+        <v>459</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>393</v>
+        <v>460</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9204,13 +9208,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9228,13 +9232,13 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
@@ -9246,13 +9250,13 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>395</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9263,10 +9267,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>397</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9277,7 +9281,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9292,15 +9296,17 @@
         <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
+        <v>468</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9324,11 +9330,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>400</v>
+        <v>472</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9346,13 +9354,13 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>397</v>
+        <v>466</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>83</v>
@@ -9364,27 +9372,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>401</v>
+        <v>464</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>402</v>
+        <v>465</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9407,19 +9415,17 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>189</v>
+        <v>474</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>406</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9444,13 +9450,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9468,7 +9474,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9489,10 +9495,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9503,10 +9509,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9529,17 +9535,15 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>414</v>
+        <v>207</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>415</v>
+        <v>480</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9588,7 +9592,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9606,27 +9610,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,7 +9641,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9646,19 +9650,19 @@
         <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>422</v>
+        <v>484</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9708,13 +9712,13 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
@@ -9726,27 +9730,27 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>426</v>
+        <v>487</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9766,23 +9770,21 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>430</v>
+        <v>170</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>431</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>431</v>
+        <v>490</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9830,7 +9832,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9842,7 +9844,7 @@
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>434</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
@@ -9851,10 +9853,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>436</v>
+        <v>492</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9865,10 +9867,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9879,7 +9881,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9888,19 +9890,23 @@
         <v>83</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>199</v>
+        <v>432</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>200</v>
+        <v>494</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -9948,19 +9954,19 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>202</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>83</v>
@@ -9969,10 +9975,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>83</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>203</v>
+        <v>498</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9983,21 +9989,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -10009,17 +10015,15 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10068,19 +10072,19 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>83</v>
@@ -10092,7 +10096,7 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10103,14 +10107,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>500</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>440</v>
+        <v>139</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10123,26 +10127,24 @@
         <v>83</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>441</v>
+        <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>442</v>
+        <v>214</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10190,7 +10192,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>217</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10214,7 +10216,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10225,42 +10227,46 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>445</v>
+        <v>140</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10308,19 +10314,19 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>448</v>
+        <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -10329,10 +10335,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>449</v>
+        <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>450</v>
+        <v>137</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10343,10 +10349,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>451</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10354,7 +10360,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>94</v>
@@ -10366,19 +10372,23 @@
         <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>445</v>
+        <v>189</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>452</v>
+        <v>503</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10402,13 +10412,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>83</v>
+        <v>292</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10426,16 +10436,16 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>451</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>448</v>
+        <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10444,16 +10454,16 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>83</v>
+        <v>506</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>449</v>
+        <v>296</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>454</v>
+        <v>297</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10461,10 +10471,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>455</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>455</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10484,22 +10494,22 @@
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>189</v>
+        <v>508</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>456</v>
+        <v>509</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>457</v>
+        <v>510</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>459</v>
+        <v>366</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10524,13 +10534,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10548,7 +10558,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>455</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10566,27 +10576,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>462</v>
+        <v>512</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>463</v>
+        <v>369</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10597,7 +10607,7 @@
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
@@ -10612,16 +10622,16 @@
         <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>467</v>
+        <v>516</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>468</v>
+        <v>375</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10646,13 +10656,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>289</v>
+        <v>376</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>469</v>
+        <v>377</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>470</v>
+        <v>378</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10670,16 +10680,16 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10688,13 +10698,13 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>462</v>
+        <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>463</v>
+        <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10705,21 +10715,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -10731,17 +10741,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>472</v>
+        <v>189</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>518</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>475</v>
+        <v>521</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10766,13 +10778,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10790,13 +10802,13 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
@@ -10808,27 +10820,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>476</v>
+        <v>390</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10839,7 +10851,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -10851,16 +10863,20 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>523</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10908,13 +10924,13 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>522</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
@@ -10929,1352 +10945,20 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP85" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP85">
+  <autoFilter ref="A1:AP74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12284,7 +10968,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
